--- a/Dear Data.xlsx
+++ b/Dear Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BE98D7-74F9-4383-82B6-A6C6DC134BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32BF2AD-046C-40AE-8F30-A2CED59A0721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{20BFF62C-E187-4311-A2FC-E57178750C95}"/>
   </bookViews>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AD3669-598C-4FCB-8B8A-D63958089B64}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" style="1" customWidth="1"/>
@@ -504,7 +504,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="B2" s="3">
         <v>5.2546296296296299E-3</v>
@@ -533,35 +533,74 @@
       <c r="J2" s="3">
         <v>3.7731481481481483E-3</v>
       </c>
+      <c r="K2" s="3">
+        <v>4.2129629629629626E-3</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46321</v>
+        <v>46319</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3.6111111111111109E-3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.7499999999999999E-3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.9699074074074072E-3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.4837962962962965E-3</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3.6111111111111109E-3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>3.1828703703703702E-3</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46322</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46323</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46324</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46325</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>46326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46327</v>
       </c>
     </row>
   </sheetData>

--- a/Dear Data.xlsx
+++ b/Dear Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32BF2AD-046C-40AE-8F30-A2CED59A0721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C9F10E-1013-4C30-9573-3186C03A0758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{20BFF62C-E187-4311-A2FC-E57178750C95}"/>
   </bookViews>
@@ -562,10 +562,34 @@
       <c r="H3" s="3">
         <v>3.1828703703703702E-3</v>
       </c>
+      <c r="I3" s="3">
+        <v>3.8773148148148148E-3</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3.3912037037037036E-3</v>
+      </c>
+      <c r="K3" s="3">
+        <v>3.6574074074074074E-3</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46320</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2.9629629629629628E-3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3.1597222222222222E-3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.0092592592592593E-3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.8657407407407408E-3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3.472222222222222E-3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">

--- a/Dear Data.xlsx
+++ b/Dear Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C9F10E-1013-4C30-9573-3186C03A0758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CC82E5-BDBE-49C2-B614-4C9172E3C320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{20BFF62C-E187-4311-A2FC-E57178750C95}"/>
   </bookViews>
@@ -591,10 +591,40 @@
       <c r="F4" s="3">
         <v>3.472222222222222E-3</v>
       </c>
+      <c r="G4" s="3">
+        <v>3.2407407407407406E-3</v>
+      </c>
+      <c r="H4" s="3">
+        <v>3.9236111111111112E-3</v>
+      </c>
+      <c r="I4" s="3">
+        <v>3.1250000000000002E-3</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3.2870370370370371E-3</v>
+      </c>
+      <c r="K4" s="3">
+        <v>3.1597222222222222E-3</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46321</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3.2175925925925926E-3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3.3449074074074076E-3</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.9861111111111113E-3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.5300925925925925E-3</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.3796296296296296E-3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
